--- a/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 4,62</t>
+          <t>-7,11; 4,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 7,07</t>
+          <t>-5,22; 6,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 4,61</t>
+          <t>-8,03; 4,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 6,35</t>
+          <t>-9,36; 6,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>-85,42; 563,05</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-78,53; 157,84</t>
+          <t>-77,59; 156,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,79</t>
+          <t>-3,08; 0,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,91</t>
+          <t>-3,81; 1,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,61</t>
+          <t>-2,05; 1,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,76</t>
+          <t>-4,71; 1,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,53; 40,35</t>
+          <t>-74,78; 48,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,09; 34,92</t>
+          <t>-67,5; 38,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,49; 138,14</t>
+          <t>-65,23; 112,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,34; 35,18</t>
+          <t>-50,49; 33,56</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; -0,64</t>
+          <t>-7,24; -0,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,19</t>
+          <t>-2,02; 2,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,79</t>
+          <t>-0,25; 7,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 2,14</t>
+          <t>-3,64; 2,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,81</t>
+          <t>-100,0; 22,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,62; 1281,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,69; 192,41</t>
+          <t>-77,86; 236,56</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,1</t>
+          <t>-3,54; -0,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,04</t>
+          <t>-2,61; 1,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,18</t>
+          <t>-1,2; 1,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,42</t>
+          <t>-3,57; 1,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,84; -0,71</t>
+          <t>-74,73; -7,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 38,77</t>
+          <t>-57,32; 43,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 138,67</t>
+          <t>-44,88; 137,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 33,56</t>
+          <t>-47,13; 25,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 4,02</t>
+          <t>-7,59; 4,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 6,33</t>
+          <t>-5,78; 6,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 4,48</t>
+          <t>-8,11; 4,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 6,81</t>
+          <t>-10,24; 6,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,42; 563,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-77,59; 156,08</t>
+          <t>-77,33; 149,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,87</t>
+          <t>-3,06; 1,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,07</t>
+          <t>-3,95; 0,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,35</t>
+          <t>-2,08; 1,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,68</t>
+          <t>-4,64; 1,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,78; 48,89</t>
+          <t>-73,94; 61,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,5; 38,23</t>
+          <t>-68,76; 32,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 112,67</t>
+          <t>-67,19; 137,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,49; 33,56</t>
+          <t>-49,35; 34,42</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,24; -0,66</t>
+          <t>-6,83; -0,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,97</t>
+          <t>-1,95; 2,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 7,18</t>
+          <t>-0,18; 6,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,51</t>
+          <t>-4,24; 2,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,2</t>
+          <t>-100,0; 34,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-57,22; 1425,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,86; 236,56</t>
+          <t>-79,36; 173,82</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,31</t>
+          <t>-3,44; -0,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,08</t>
+          <t>-2,45; 1,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,97</t>
+          <t>-1,13; 1,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,18</t>
+          <t>-3,58; 1,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,73; -7,79</t>
+          <t>-74,46; -2,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 43,35</t>
+          <t>-55,34; 42,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 137,13</t>
+          <t>-38,88; 127,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 25,38</t>
+          <t>-45,85; 25,84</t>
         </is>
       </c>
     </row>
